--- a/artfynd/A 57471-2025 artfynd.xlsx
+++ b/artfynd/A 57471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88851538</v>
+        <v>88851529</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455836.412211553</v>
+        <v>455874</v>
       </c>
       <c r="R2" t="n">
-        <v>6660799.097435662</v>
+        <v>6660780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,11 +760,6 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88851543</v>
+        <v>88851532</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455840.7281079874</v>
+        <v>455876</v>
       </c>
       <c r="R3" t="n">
-        <v>6660825.494190284</v>
+        <v>6660738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,21 +845,11 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -897,11 +862,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,50 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88851546</v>
+        <v>118870547</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder Omsjön, Vrm</t>
+          <t>Bratthöjdsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455791.8264093636</v>
+        <v>455873</v>
       </c>
       <c r="R4" t="n">
-        <v>6660832.56904747</v>
+        <v>6660797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,41 +960,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88851532</v>
+        <v>118870549</v>
       </c>
       <c r="B5" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,14 +1007,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder Omsjön, Vrm</t>
+          <t>Bratthöjdsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455876.1653884602</v>
+        <v>455889</v>
       </c>
       <c r="R5" t="n">
-        <v>6660737.737939904</v>
+        <v>6660732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,71 +1057,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88851539</v>
+        <v>118870553</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söder Omsjön, Vrm</t>
+          <t>Bratthöjdsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455840.1324572367</v>
+        <v>455788</v>
       </c>
       <c r="R6" t="n">
-        <v>6660817.516885852</v>
+        <v>6660704</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,22 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,45 +1154,30 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88851542</v>
+        <v>88851530</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1320,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455835.8620005647</v>
+        <v>455870</v>
       </c>
       <c r="R7" t="n">
-        <v>6660836.531221618</v>
+        <v>6660725</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,19 +1238,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,19 +1277,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88851533</v>
+        <v>88851531</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1442,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455878.164606354</v>
+        <v>455877</v>
       </c>
       <c r="R8" t="n">
-        <v>6660737.713955468</v>
+        <v>6660723</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,19 +1345,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,19 +1384,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88851544</v>
+        <v>88851533</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1564,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455832.1657200293</v>
+        <v>455878</v>
       </c>
       <c r="R9" t="n">
-        <v>6660820.107698313</v>
+        <v>6660738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,19 +1452,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,16 +1494,11 @@
         <v>88851534</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1686,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455875.6895290902</v>
+        <v>455876</v>
       </c>
       <c r="R10" t="n">
-        <v>6660739.739807267</v>
+        <v>6660740</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,19 +1559,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,19 +1598,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88851541</v>
+        <v>88851535</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1808,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455838.8607469839</v>
+        <v>455869</v>
       </c>
       <c r="R11" t="n">
-        <v>6660836.495212185</v>
+        <v>6660762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,19 +1666,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,16 +1708,11 @@
         <v>88851536</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1930,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455854.3869059074</v>
+        <v>455854</v>
       </c>
       <c r="R12" t="n">
-        <v>6660797.384539915</v>
+        <v>6660797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1963,19 +1773,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2012,37 +1812,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>88851529</v>
+        <v>88851537</v>
       </c>
       <c r="B13" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2052,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455873.6694354447</v>
+        <v>455828</v>
       </c>
       <c r="R13" t="n">
-        <v>6660779.686984409</v>
+        <v>6660797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2085,21 +1880,11 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2112,6 +1897,11 @@
       <c r="AI13" t="inlineStr">
         <is>
           <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2129,19 +1919,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88851531</v>
+        <v>88851538</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2169,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455876.9854149686</v>
+        <v>455836</v>
       </c>
       <c r="R14" t="n">
-        <v>6660722.756879967</v>
+        <v>6660799</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,19 +1987,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,19 +2026,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>88851537</v>
+        <v>88851539</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2291,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455828.3915022531</v>
+        <v>455840</v>
       </c>
       <c r="R15" t="n">
-        <v>6660797.197632222</v>
+        <v>6660818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,19 +2094,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2376,16 +2136,11 @@
         <v>88851540</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2413,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455840.1803863467</v>
+        <v>455840</v>
       </c>
       <c r="R16" t="n">
-        <v>6660821.508540798</v>
+        <v>6660822</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,19 +2201,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2495,37 +2240,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>88851545</v>
+        <v>88851541</v>
       </c>
       <c r="B17" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2535,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455832.1657200293</v>
+        <v>455839</v>
       </c>
       <c r="R17" t="n">
-        <v>6660820.107698313</v>
+        <v>6660836</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,21 +2308,11 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2599,7 +2329,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2617,19 +2347,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>88851535</v>
+        <v>88851542</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2657,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455869.4555088693</v>
+        <v>455836</v>
       </c>
       <c r="R18" t="n">
-        <v>6660761.7722754</v>
+        <v>6660837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2690,19 +2415,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,19 +2454,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>88851530</v>
+        <v>88851543</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2779,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455870.0120720632</v>
+        <v>455841</v>
       </c>
       <c r="R19" t="n">
-        <v>6660724.836711537</v>
+        <v>6660825</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2812,19 +2522,9 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-04-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2861,19 +2561,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118870543</v>
+        <v>88851544</v>
       </c>
       <c r="B20" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2897,14 +2592,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bratthöjdsmossen, Vrm</t>
+          <t>Söder Omsjön, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455881</v>
+        <v>455832</v>
       </c>
       <c r="R20" t="n">
-        <v>6660874</v>
+        <v>6660820</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2931,12 +2626,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2947,71 +2642,71 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118870551</v>
+        <v>88851546</v>
       </c>
       <c r="B21" t="n">
-        <v>5186</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bratthöjdsmossen, Vrm</t>
+          <t>Söder Omsjön, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455866</v>
+        <v>455792</v>
       </c>
       <c r="R21" t="n">
-        <v>6660755</v>
+        <v>6660833</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3038,12 +2733,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,66 +2749,71 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118870546</v>
+        <v>88851547</v>
       </c>
       <c r="B22" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bratthöjdsmossen, Vrm</t>
+          <t>Söder Omsjön, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455855</v>
+        <v>455655</v>
       </c>
       <c r="R22" t="n">
-        <v>6660813</v>
+        <v>6660820</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3140,12 +2840,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3156,35 +2856,40 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118870550</v>
+        <v>88851549</v>
       </c>
       <c r="B23" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3208,14 +2913,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bratthöjdsmossen, Vrm</t>
+          <t>Söder Omsjön, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455875</v>
+        <v>455657</v>
       </c>
       <c r="R23" t="n">
-        <v>6660735</v>
+        <v>6660829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3242,12 +2947,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3258,66 +2963,71 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118870547</v>
+        <v>88851550</v>
       </c>
       <c r="B24" t="n">
-        <v>95153</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bratthöjdsmossen, Vrm</t>
+          <t>Söder Omsjön, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455873</v>
+        <v>455652</v>
       </c>
       <c r="R24" t="n">
-        <v>6660797</v>
+        <v>6660866</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3344,12 +3054,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3360,35 +3070,40 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118870544</v>
+        <v>88851551</v>
       </c>
       <c r="B25" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3412,14 +3127,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bratthöjdsmossen, Vrm</t>
+          <t>Söder Omsjön, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455845</v>
+        <v>455654</v>
       </c>
       <c r="R25" t="n">
-        <v>6660895</v>
+        <v>6660872</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3446,12 +3161,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,53 +3177,58 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118870549</v>
+        <v>118870539</v>
       </c>
       <c r="B26" t="n">
-        <v>95153</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3518,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455889</v>
+        <v>455875</v>
       </c>
       <c r="R26" t="n">
-        <v>6660732</v>
+        <v>6660825</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3580,19 +3300,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118870545</v>
+        <v>118870540</v>
       </c>
       <c r="B27" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3620,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455771</v>
+        <v>455878</v>
       </c>
       <c r="R27" t="n">
-        <v>6660888</v>
+        <v>6660833</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3682,19 +3397,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118870540</v>
+        <v>118870541</v>
       </c>
       <c r="B28" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3722,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455878</v>
+        <v>455889</v>
       </c>
       <c r="R28" t="n">
-        <v>6660833</v>
+        <v>6660852</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3784,37 +3494,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118870553</v>
+        <v>118870542</v>
       </c>
       <c r="B29" t="n">
-        <v>95153</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3824,10 +3529,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455788</v>
+        <v>455886</v>
       </c>
       <c r="R29" t="n">
-        <v>6660704</v>
+        <v>6660861</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3886,19 +3591,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118870542</v>
+        <v>118870543</v>
       </c>
       <c r="B30" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3926,10 +3626,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455886</v>
+        <v>455881</v>
       </c>
       <c r="R30" t="n">
-        <v>6660861</v>
+        <v>6660874</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3988,19 +3688,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118870539</v>
+        <v>118870544</v>
       </c>
       <c r="B31" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4028,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455875</v>
+        <v>455845</v>
       </c>
       <c r="R31" t="n">
-        <v>6660825</v>
+        <v>6660895</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4090,19 +3785,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118870548</v>
+        <v>118870545</v>
       </c>
       <c r="B32" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4130,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455873</v>
+        <v>455771</v>
       </c>
       <c r="R32" t="n">
-        <v>6660787</v>
+        <v>6660888</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4192,19 +3882,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118870541</v>
+        <v>118870548</v>
       </c>
       <c r="B33" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4232,10 +3917,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455889</v>
+        <v>455873</v>
       </c>
       <c r="R33" t="n">
-        <v>6660852</v>
+        <v>6660787</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,6 +3976,409 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118870550</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bratthöjdsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>455875</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6660735</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gåsborn</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>88851545</v>
+      </c>
+      <c r="B35" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Söder Omsjön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>455832</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6660820</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gåsborn</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2020-04-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2020-04-05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Barrblandskog som är naturligt föryngrad för ca 100 år sedan med inslag av äldre träd och död ved.</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118870551</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bratthöjdsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>455866</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6660755</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gåsborn</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118870546</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bratthöjdsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>455855</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6660813</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gåsborn</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57471-2025 artfynd.xlsx
+++ b/artfynd/A 57471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851532</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870547</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870549</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870553</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851530</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851531</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851533</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851534</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851535</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851536</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851537</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851538</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851539</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851540</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851541</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2451,6 +2536,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851542</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851543</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851544</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851546</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2879,6 +2984,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851547</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2986,6 +3096,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851549</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3093,6 +3208,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851550</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3200,6 +3320,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851551</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3297,6 +3422,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870539</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3394,6 +3524,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870540</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3491,6 +3626,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870541</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3588,6 +3728,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870542</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3685,6 +3830,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870543</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3782,6 +3932,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870544</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3879,6 +4034,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870545</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3976,6 +4136,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870548</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4073,6 +4238,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870550</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4180,6 +4350,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88851545</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4282,6 +4457,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870551</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4379,8 +4559,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118870546</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>